--- a/sample-report/stakeholder-review-finalists.xlsx
+++ b/sample-report/stakeholder-review-finalists.xlsx
@@ -7913,7 +7913,16 @@
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>OWASP Top 10 and OWASP API Security Top 10 mapping confirmed; no explicit PCI-DSS/GLBA/SOX/FFIEC/NYDFS regulatory-framework mapping found in DAST-specific documentation, though the platform broadly targets enterprise/regulated customers.</t>
+          <r>
+            <t xml:space="preserve">OWASP Top 10 and OWASP API Security Top 10 mapping confirmed; no explicit PCI-DSS/GLBA/SOX/FFIEC/NYDFS regulatory-framework mapping found in DAST-specific documentation, though the platform broadly targets enterprise/regulated customers. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>checkmarx.com/learn/integrating-dast-and-sast-into-devsecops-for-continuous-api-security</t>
+          </r>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -7975,7 +7984,16 @@
       </c>
       <c r="E13" s="18" t="inlineStr">
         <is>
-          <t>Proof-based scanning validates findings before flagging, and SAST-DAST correlation is cited to reduce noise -- but the vendor's own '89% noise reduction' figure applies to platform-wide ASPM correlation across all scanners, not a DAST-isolated false-positive rate, so it's cited here with that caveat rather than at face value.</t>
+          <r>
+            <t xml:space="preserve">Proof-based scanning validates findings before flagging, and SAST-DAST correlation is cited to reduce noise -- but the vendor's own '89% noise reduction' figure applies to platform-wide ASPM correlation across all scanners, not a DAST-isolated false-positive rate, so it's cited here with that caveat rather than at face value. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>checkmarx.com/blog/checkmarx-dast-for-the-ai-coding-era</t>
+          </r>
         </is>
       </c>
       <c r="F13" s="16" t="inlineStr">
@@ -10155,29 +10173,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11949,7 +11969,16 @@
       </c>
       <c r="E25" s="18" t="inlineStr">
         <is>
-          <t>AppScan on Cloud aggregates and correlates DAST, SAST, and IAST findings to provide proof of exploitability, prioritizing the most critical confirmed issues. Source: general platform documentation</t>
+          <r>
+            <t xml:space="preserve">AppScan on Cloud aggregates and correlates DAST, SAST, and IAST findings to provide proof of exploitability, prioritizing the most critical confirmed issues. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>hcl-software.com/appscan</t>
+          </r>
         </is>
       </c>
       <c r="F25" s="16" t="inlineStr">
@@ -12449,7 +12478,16 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>API-level discovery/inventory confirmed via the Salt Security partnership; not confirmed at the rubric's top tier of scanning public IP ranges/domains for rogue unmapped apps.</t>
+          <r>
+            <t xml:space="preserve">API-level discovery/inventory confirmed via the Salt Security partnership; not confirmed at the rubric's top tier of scanning public IP ranges/domains for rogue unmapped apps. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>hcl-software.com/appscan/products/api-security</t>
+          </r>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
@@ -13288,16 +13326,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sample-report/stakeholder-review-finalists.xlsx
+++ b/sample-report/stakeholder-review-finalists.xlsx
@@ -1403,11 +1403,23 @@
         <v>6</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>No explicit passive-only/rate-limited safe-mode messaging found in public materials, though Proof-Based Scanning's non-destructive verification implies some inherent caution -- inferred, moderate confidence.</t>
+          <r>
+            <t xml:space="preserve">Revised up with real citations: a dedicated 'Scanning Production Environments' guide exists, passive security checks issue no extra HTTP requests, and scan speed is configurable across four tiers (Sequential/Slow/Moderate/Fast) specifically to handle rate-limited/production environments -- more concrete than initially found, though Invicti's own docs still caveat that active checks can be invasive even though non-destructive. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>invicti.com/support/scanning-production-environment</t>
+          </r>
+          <r>
+            <t>, docs.invicti.com/ip/target-scan-configuration</t>
+          </r>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
@@ -1688,7 +1700,19 @@
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>SOAP API scanning explicitly supported; no legacy-framework-specific (ASP WebForms/JSP) accuracy claims found beyond general protocol coverage.</t>
+          <r>
+            <t xml:space="preserve">SOAP API scanning explicitly supported via WSDL schema parsing (file or URL), and </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>ASP.NET</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> applications are explicitly detected/supported including JS-heavy interfaces; no JSP-specific accuracy claims found beyond general protocol coverage. Source: invicti.com/soap-scanner, invicti.com/web-vulnerability-scanner/vulnerabilities/aspnet-identified</t>
+          </r>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
@@ -2250,7 +2274,16 @@
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Licensed per-target (web app, API endpoint, or defined URL scope) across Standard/Premium/Enterprise tiers -- a clear, transparent axis, but Enterprise-tier pricing is fully customized/contact-sales, and approximate price ranges ($4k-6k Standard, $7k-12k Premium per target/year) come from third-party pricing aggregators, not Invicti's own published pricing page.</t>
+          <r>
+            <t xml:space="preserve">Licensed per-target (web app, API endpoint, or defined URL scope) across Standard/Premium/Enterprise tiers -- a clear, transparent axis -- but Enterprise-tier pricing is fully customized/contact-sales, and independent market data shows real-world deals commonly landing at $15,000-25,000+/year once RBAC/SCA/ASPM/on-prem/support are bundled in, well above the $4k-6k Standard-tier estimates quoted by third-party pricing aggregators (not Invicti's own published pricing page). Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>beaglesecurity.com/blog/article/invicti-pricing</t>
+          </r>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -2312,7 +2345,16 @@
       </c>
       <c r="E19" s="18" t="inlineStr">
         <is>
-          <t>Role-based access control explicitly marketed as part of its enterprise-focused platform, described as 'broader RBAC' relative to smaller competitors; audit-log capability not independently confirmed.</t>
+          <r>
+            <t xml:space="preserve">RBAC and Custom Roles are explicitly listed as Enterprise-edition features, marketed as 'broader RBAC' relative to smaller competitors; a dedicated audit-log capability was not independently confirmed in public materials. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>appsecsanta.com/invicti</t>
+          </r>
         </is>
       </c>
       <c r="F19" s="16" t="inlineStr">
@@ -2374,7 +2416,16 @@
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Enterprise-platform positioning (dedicated account management, custom SLAs, on-prem deployment options) implies moderate setup complexity, more involved than a single docker-pull tool -- inferred from tier positioning, no explicit onboarding-time claim found.</t>
+          <r>
+            <t xml:space="preserve">Invicti's own recommended rollout plan allocates Days 1-10 of a 30-day implementation plan to onboarding, configuring, and prioritizing the first set of web apps/APIs -- moderate enterprise-platform setup complexity, not a minutes-to-first-scan tool, consistent with its enterprise positioning. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>invicti.com/support/invicti-quick-start-guide</t>
+          </r>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
@@ -2938,11 +2989,23 @@
         <v>2</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Enterprise tier implies scale (unlimited seats, custom SLAs, dedicated account management) but no explicit scan-speed or concurrency benchmark found in public materials -- inferred from tier positioning.</t>
+          <r>
+            <t xml:space="preserve">Revised up with real citations: configurable speed tiers (Sequential/Slow/Moderate/Fast, default Fast), plus a documented performance upgrade claiming up to 150% faster vulnerability discovery via dynamic resource allocation -- but independent commentary notes scalability challenges (resource consumption, longer scan times) when running many concurrent scanning agents across a large application portfolio. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>invicti.com/blog/web-security/netsparker-scan-performance-upgrades</t>
+          </r>
+          <r>
+            <t>, docs.invicti.com/ip/target-scan-configuration</t>
+          </r>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
@@ -3226,7 +3289,19 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>No dedicated vendor-risk-assessment output shaping for partner-facing APIs found in public materials -- inferred absence.</t>
+          <r>
+            <t xml:space="preserve">No dedicated vendor-risk-assessment output shaping for partner-facing APIs found in public materials -- inferred absence. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>invicti.com/solutions/financial-services</t>
+          </r>
+          <r>
+            <t>, docs.invicti.com/ie-is/manage-api-inventory (API Inventory filters only by source/scan date/target/type, no partner-risk categorization)</t>
+          </r>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
@@ -3355,11 +3430,20 @@
         <v>1</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>SIEM integration mentioned generally as part of its broader toolchain integrations, but no specific named platforms (e.g. Splunk, Elasticsearch) confirmed in public materials.</t>
+          <r>
+            <t xml:space="preserve">Revised up with a real citation: a dedicated, unified Invicti Enterprise add-on for Splunk (supporting both Splunk Enterprise on-prem and Splunk Cloud) is published on Splunkbase -- a confirmed native SIEM integration, though no QRadar or Microsoft Sentinel integration was found. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>docs.invicti.com/ie-is/invicti-enterprise-addon-splunk</t>
+          </r>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
@@ -4028,29 +4112,37 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4286,7 +4378,19 @@
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>No specific detection-rate benchmark found in public materials; inferred from general enterprise reputation as an established SAST/DAST/SCA platform, not a specific accuracy claim.</t>
+          <r>
+            <t xml:space="preserve">No specific independent detection-rate benchmark found for Veracode's DAST specifically; scored from general enterprise-platform positioning and market recognition (a 9x Gartner Magic Quadrant Leader for Application Security Testing) rather than a cited accuracy number. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>veracode.com/products/dynamic-analysis-dast</t>
+          </r>
+          <r>
+            <t>, securityscientist.net/blog/12-questions-and-answers-about-veracode-dast</t>
+          </r>
         </is>
       </c>
       <c r="F4" s="11" t="inlineStr">
@@ -5804,7 +5908,19 @@
       </c>
       <c r="E25" s="18" t="inlineStr">
         <is>
-          <t>No dedicated financial-data-pattern (account/routing number, card PAN) detection capability found -- inferred absence.</t>
+          <r>
+            <t xml:space="preserve">No dedicated financial-data-pattern (account/routing number, card PAN) detection capability found -- inferred absence. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>docs.veracode.com/r/c_review_cwe</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (only generic sensitive-data-exposure CWEs found, CWE-200/201/359 family; no dedicated financial-pattern detector for PANs/routing numbers/SSNs)</t>
+          </r>
         </is>
       </c>
       <c r="F25" s="16" t="inlineStr">
@@ -5862,11 +5978,20 @@
         <v>2</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>No dedicated proof-of-exploit/safe-re-exploitation engine found (unlike Invicti's Proof-Based Scanning); DAST's dynamic/behavioral nature gives some inherent evidence over static pattern matching, but no explicit confirmation-engine claim.</t>
+          <r>
+            <t xml:space="preserve">Revised up with a real citation: clicking a finding in Veracode DAST Essentials surfaces the exact payload used for the exploit, and findings can be independently replicated via a generated curl request -- a concrete proof-of-exploit mechanism comparable to other proof-based scanners, not just an inherent dynamic-testing advantage over static pattern matching. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>veracode.com/blog/getting-started-guide-veracode-dast-essentials</t>
+          </r>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
@@ -6215,7 +6340,19 @@
       </c>
       <c r="E31" s="18" t="inlineStr">
         <is>
-          <t>Community integration tooling (Veracode-Community-Projects) exists for automation/glue, but no detection-rule-authoring DSL comparable to ZAP's Zest or Nuclei's YAML templates found.</t>
+          <r>
+            <t xml:space="preserve">Community integration tooling (Veracode-Community-Projects) exists for automation/glue, but no detection-rule-authoring DSL comparable to ZAP's Zest or Nuclei's YAML templates found. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>docs.veracode.com/r/c_sc_policies_custom</t>
+          </r>
+          <r>
+            <t>, docs.veracode.com/r/Create_Custom_Rules_for_Agent_Based_Scanning (custom rules found are for SCA agent-based scanning license/component policy controls, not new DAST detection signatures)</t>
+          </r>
         </is>
       </c>
       <c r="F31" s="16" t="inlineStr">
@@ -6277,7 +6414,19 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>No confirmed native SIEM/SOAR integration found in research -- explicitly a research gap rather than a confirmed absence; only community Slack-webhook-redirect tooling for SCA agent results was found.</t>
+          <r>
+            <t xml:space="preserve">No confirmed native SIEM/SOAR integration found in research -- explicitly a research gap rather than a confirmed absence; only community Slack-webhook-redirect tooling for SCA agent results was found. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>docs.veracode.com/r/Veracode_Integrations</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (official integrations page lists Jira/Bugzilla/RSA Archer/Imperva/CI-CD/IDE tools, no native Splunk/QRadar/Sentinel/XSOAR), splunkbase.splunk.com/app/7277 ('Veracode Splunk Bridge' is third-party/community-built, not Veracode-authored)</t>
+          </r>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
@@ -6339,7 +6488,19 @@
       </c>
       <c r="E33" s="18" t="inlineStr">
         <is>
-          <t>No dedicated vendor-risk-assessment output shaping for partner-facing APIs found -- inferred absence.</t>
+          <r>
+            <t xml:space="preserve">No dedicated vendor-risk-assessment output shaping for partner-facing APIs found -- inferred absence. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>veracode.com/security/third-party-risk-assessment</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (Veracode's 'third-party risk' products, SCA/VAST, address risk from vendors' code coming in, not risk of your APIs facing partners -- opposite direction from the rubric)</t>
+          </r>
         </is>
       </c>
       <c r="F33" s="16" t="inlineStr">
@@ -7080,33 +7241,39 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7342,7 +7509,19 @@
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>Comprehensive OWASP Top 10 and OWASP API Top 10 coverage claimed, plus business-logic-aware testing -- but no independently published benchmark/ground-truth accuracy score found. Paper confidence, inferred from platform positioning rather than a cited third-party benchmark.</t>
+          <r>
+            <t xml:space="preserve">Comprehensive OWASP Top 10 and OWASP API Top 10 coverage claimed, plus business-logic-aware testing -- but no independently published benchmark/ground-truth accuracy score found. Paper confidence, inferred from platform positioning rather than a cited third-party benchmark. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>checkmarx.com/checkmarx-dast</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (vendor's own general accuracy/coverage claim, not an independent benchmark)</t>
+          </r>
         </is>
       </c>
       <c r="F4" s="11" t="inlineStr">
@@ -10166,38 +10345,39 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
